--- a/Ecslearn/config/excel/upgrades.xlsx
+++ b/Ecslearn/config/excel/upgrades.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G28"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -437,10 +437,10 @@
         <v>rapid-fire</v>
       </c>
       <c r="B2" t="str">
-        <v>急速弓弦</v>
+        <v>急速连射</v>
       </c>
       <c r="C2" t="str">
-        <v>攻速+30%</v>
+        <v>攻速+20%</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -457,13 +457,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>power-strike</v>
+        <v>arrow-speed</v>
       </c>
       <c r="B3" t="str">
-        <v>锐利箭头</v>
+        <v>箭矢轻量化</v>
       </c>
       <c r="C3" t="str">
-        <v>攻击+30%</v>
+        <v>箭速+40%</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -480,13 +480,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>long-range</v>
+        <v>sharp-arrow</v>
       </c>
       <c r="B4" t="str">
-        <v>远程瞄准</v>
+        <v>锐利箭头</v>
       </c>
       <c r="C4" t="str">
-        <v>射程+50%</v>
+        <v>攻击+30%</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -503,13 +503,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>pierce-shot</v>
+        <v>lifesteal</v>
       </c>
       <c r="B5" t="str">
-        <v>穿透射击</v>
+        <v>生命汲取</v>
       </c>
       <c r="C5" t="str">
-        <v>穿透+1</v>
+        <v>吸血率+8%</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -518,7 +518,7 @@
         <v>common</v>
       </c>
       <c r="F5" t="str">
-        <v>proj</v>
+        <v>attr</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -526,22 +526,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>multi-shot</v>
+        <v>knockback</v>
       </c>
       <c r="B6" t="str">
-        <v>多重射击</v>
+        <v>击退之力</v>
       </c>
       <c r="C6" t="str">
-        <v>弹道+1</v>
+        <v>命中击退敌人</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="str">
-        <v>rare</v>
+        <v>common</v>
       </c>
       <c r="F6" t="str">
-        <v>proj</v>
+        <v>onhit</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -549,13 +549,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bounce-shot</v>
+        <v>fire-arrow</v>
       </c>
       <c r="B7" t="str">
-        <v>弹射之弓</v>
+        <v>烈焰箭</v>
       </c>
       <c r="C7" t="str">
-        <v>弹射+1</v>
+        <v>命中施加灼烧DOT(ATK×20%/3s)</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -564,7 +564,7 @@
         <v>rare</v>
       </c>
       <c r="F7" t="str">
-        <v>proj</v>
+        <v>onhit</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -572,19 +572,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>fire-arrow</v>
+        <v>frost-arrow</v>
       </c>
       <c r="B8" t="str">
-        <v>烈焰箭</v>
+        <v>寒冰箭</v>
       </c>
       <c r="C8" t="str">
-        <v>命中施加灼烧 DOT</v>
+        <v>命中减速30%/2s，叠3层冰冻</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="str">
-        <v>common</v>
+        <v>rare</v>
       </c>
       <c r="F8" t="str">
         <v>onhit</v>
@@ -595,13 +595,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>frost-arrow</v>
+        <v>crit-instinct</v>
       </c>
       <c r="B9" t="str">
-        <v>寒冰箭</v>
+        <v>暴击直觉</v>
       </c>
       <c r="C9" t="str">
-        <v>命中施加冻伤减速</v>
+        <v>暴击率+10%</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -610,7 +610,7 @@
         <v>common</v>
       </c>
       <c r="F9" t="str">
-        <v>onhit</v>
+        <v>attr</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -618,22 +618,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>lightning-arrow</v>
+        <v>swift-step</v>
       </c>
       <c r="B10" t="str">
-        <v>雷电箭</v>
+        <v>疾风步</v>
       </c>
       <c r="C10" t="str">
-        <v>命中触发闪电链</v>
+        <v>移速+20%</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>rare</v>
+        <v>common</v>
       </c>
       <c r="F10" t="str">
-        <v>onhit</v>
+        <v>attr</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -641,22 +641,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>auto-fire-1</v>
+        <v>multi-shot</v>
       </c>
       <c r="B11" t="str">
-        <v>自动速射 Lv1</v>
+        <v>多重射击</v>
       </c>
       <c r="C11" t="str">
-        <v>静止时自动射击</v>
+        <v>额外弹道+1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="str">
-        <v>common</v>
+        <v>rare</v>
       </c>
       <c r="F11" t="str">
-        <v>policy</v>
+        <v>proj</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -664,13 +664,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>auto-fire-2</v>
+        <v>pierce-shot</v>
       </c>
       <c r="B12" t="str">
-        <v>自动速射 Lv2</v>
+        <v>穿透射击</v>
       </c>
       <c r="C12" t="str">
-        <v>移动中也自动射击</v>
+        <v>穿透+2</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -679,7 +679,7 @@
         <v>rare</v>
       </c>
       <c r="F12" t="str">
-        <v>policy</v>
+        <v>proj</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -687,22 +687,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>auto-fire-3</v>
+        <v>lightning-arrow</v>
       </c>
       <c r="B13" t="str">
-        <v>自动速射 Lv3</v>
+        <v>雷电箭</v>
       </c>
       <c r="C13" t="str">
-        <v>始终自动射击（含无目标）</v>
+        <v>命中100%触发闪电链(3跳)</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>epic</v>
       </c>
       <c r="F13" t="str">
-        <v>policy</v>
+        <v>onhit</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -710,13 +710,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>scorching-pierce</v>
+        <v>barrage-shot</v>
       </c>
       <c r="B14" t="str">
-        <v>灼热穿刺</v>
+        <v>弹幕射手</v>
       </c>
       <c r="C14" t="str">
-        <v>穿透+灼烧 → 火线穿刺</v>
+        <v>额外弹道+2(扇形散开)</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -725,22 +725,344 @@
         <v>epic</v>
       </c>
       <c r="F14" t="str">
-        <v>onhit</v>
+        <v>proj</v>
       </c>
       <c r="G14" t="str">
-        <v>fire-arrow,pierce-shot</v>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>spread-mode</v>
+      </c>
+      <c r="B15" t="str">
+        <v>扫射模式</v>
+      </c>
+      <c r="C15" t="str">
+        <v>扇形角度+45°</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="str">
+        <v>rare</v>
+      </c>
+      <c r="F15" t="str">
+        <v>proj</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>chain-bounce</v>
+      </c>
+      <c r="B16" t="str">
+        <v>连锁弹射</v>
+      </c>
+      <c r="C16" t="str">
+        <v>弹射+4次(不衰减)</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F16" t="str">
+        <v>proj</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>long-range</v>
+      </c>
+      <c r="B17" t="str">
+        <v>远程瞄准</v>
+      </c>
+      <c r="C17" t="str">
+        <v>射程+50%</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17" t="str">
+        <v>common</v>
+      </c>
+      <c r="F17" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>rapid-fire-2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>急速连射 II</v>
+      </c>
+      <c r="C18" t="str">
+        <v>攻速+30%</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="str">
+        <v>rare</v>
+      </c>
+      <c r="F18" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>sharp-arrow-2</v>
+      </c>
+      <c r="B19" t="str">
+        <v>锐利箭头 II</v>
+      </c>
+      <c r="C19" t="str">
+        <v>攻击+50%</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="str">
+        <v>rare</v>
+      </c>
+      <c r="F19" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>infinite-pierce</v>
+      </c>
+      <c r="B20" t="str">
+        <v>无限穿透</v>
+      </c>
+      <c r="C20" t="str">
+        <v>穿透+5(不衰减)</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F20" t="str">
+        <v>proj</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>homing-instinct</v>
+      </c>
+      <c r="B21" t="str">
+        <v>追猎本能</v>
+      </c>
+      <c r="C21" t="str">
+        <v>强追踪(转向×3)</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F21" t="str">
+        <v>proj</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>barrage-shot-2</v>
+      </c>
+      <c r="B22" t="str">
+        <v>弹幕射手 II</v>
+      </c>
+      <c r="C22" t="str">
+        <v>额外弹道+3</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F22" t="str">
+        <v>proj</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>chain-bounce-2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>连锁弹射 II</v>
+      </c>
+      <c r="C23" t="str">
+        <v>弹射+6次</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F23" t="str">
+        <v>proj</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>crit-storm</v>
+      </c>
+      <c r="B24" t="str">
+        <v>暴击风暴</v>
+      </c>
+      <c r="C24" t="str">
+        <v>暴击率+25%，暴击伤害+50%</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F24" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>executioner</v>
+      </c>
+      <c r="B25" t="str">
+        <v>处刑之箭</v>
+      </c>
+      <c r="C25" t="str">
+        <v>攻击+80%(对低血量更强)</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="str">
+        <v>legendary</v>
+      </c>
+      <c r="F25" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>rapid-fire-3</v>
+      </c>
+      <c r="B26" t="str">
+        <v>急速连射 III</v>
+      </c>
+      <c r="C26" t="str">
+        <v>攻速+50%</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F26" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>sharp-arrow-3</v>
+      </c>
+      <c r="B27" t="str">
+        <v>锐利箭头 III</v>
+      </c>
+      <c r="C27" t="str">
+        <v>攻击+80%</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" t="str">
+        <v>epic</v>
+      </c>
+      <c r="F27" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>lifesteal-2</v>
+      </c>
+      <c r="B28" t="str">
+        <v>生命汲取 II</v>
+      </c>
+      <c r="C28" t="str">
+        <v>吸血率+15%</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="str">
+        <v>rare</v>
+      </c>
+      <c r="F28" t="str">
+        <v>attr</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L29"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -802,13 +1124,13 @@
         <v>buff</v>
       </c>
       <c r="C2">
-        <v>7001</v>
+        <v>2101</v>
       </c>
       <c r="D2" t="str">
         <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E2" t="str">
-        <v>急速弓弦</v>
+        <v>急速连射</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -820,7 +1142,7 @@
         <v>AttackSpeed-Mul-Buff</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -834,19 +1156,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>power-strike</v>
+        <v>arrow-speed</v>
       </c>
       <c r="B3" t="str">
         <v>buff</v>
       </c>
       <c r="C3">
-        <v>7002</v>
+        <v>2102</v>
       </c>
       <c r="D3" t="str">
         <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E3" t="str">
-        <v>锐利箭头</v>
+        <v>箭矢轻量化</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -855,10 +1177,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="str">
-        <v>Attack-Mul-Buff</v>
+        <v>ArrowSpeed-Mul-Buff</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -872,19 +1194,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>long-range</v>
+        <v>sharp-arrow</v>
       </c>
       <c r="B4" t="str">
         <v>buff</v>
       </c>
       <c r="C4">
-        <v>7003</v>
+        <v>2201</v>
       </c>
       <c r="D4" t="str">
         <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E4" t="str">
-        <v>远程瞄准</v>
+        <v>锐利箭头</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -893,10 +1215,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="str">
-        <v>AttackRange-Mul-Buff</v>
+        <v>Attack-Mul-Buff</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -910,19 +1232,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>pierce-shot</v>
+        <v>lifesteal</v>
       </c>
       <c r="B5" t="str">
         <v>buff</v>
       </c>
       <c r="C5">
-        <v>7101</v>
+        <v>2202</v>
       </c>
       <c r="D5" t="str">
         <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E5" t="str">
-        <v>穿透射击</v>
+        <v>生命汲取</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -931,10 +1253,10 @@
         <v>1</v>
       </c>
       <c r="H5" t="str">
-        <v>PierceCount-Value-Buff</v>
+        <v>LifestealRate-Value-Buff</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.08</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -948,92 +1270,92 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>multi-shot</v>
+        <v>knockback</v>
       </c>
       <c r="B6" t="str">
-        <v>buff</v>
-      </c>
-      <c r="C6">
-        <v>7102</v>
+        <v>hit_effect</v>
+      </c>
+      <c r="C6" t="str">
+        <v>upg-knockback</v>
       </c>
       <c r="D6" t="str">
-        <v>SimpleAttrBuffEffect</v>
+        <v>KnockbackEffect</v>
       </c>
       <c r="E6" t="str">
-        <v>多重射击</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>ExtraProjectiles-Value-Buff</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6">
+        <v>90</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>knockDist=60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bounce-shot</v>
+        <v>fire-arrow</v>
       </c>
       <c r="B7" t="str">
-        <v>buff</v>
-      </c>
-      <c r="C7">
-        <v>7103</v>
+        <v>hit_effect</v>
+      </c>
+      <c r="C7" t="str">
+        <v>upg-burn</v>
       </c>
       <c r="D7" t="str">
-        <v>SimpleAttrBuffEffect</v>
+        <v>BurnOnHitEffect</v>
       </c>
       <c r="E7" t="str">
-        <v>弹射之弓</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>BounceCount-Value-Buff</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7">
+        <v>50</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>burnRatio=0.2;burnBuffId=8001;burnDuration=3;burnTickInterval=0.5;burnMaxStack=5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>fire-arrow</v>
+        <v>frost-arrow</v>
       </c>
       <c r="B8" t="str">
         <v>hit_effect</v>
       </c>
       <c r="C8" t="str">
-        <v>upg-burn</v>
+        <v>upg-frost</v>
       </c>
       <c r="D8" t="str">
-        <v>BurnOnHitEffect</v>
+        <v>FrostOnHitEffect</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1057,118 +1379,118 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>burnRatio=0.2;burnBuffId=8001;burnDuration=5</v>
+        <v>frostBuffId=8101;frostSlowPerStack=0.3;frostDuration=2;frostMaxStack=3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>frost-arrow</v>
+        <v>crit-instinct</v>
       </c>
       <c r="B9" t="str">
-        <v>hit_effect</v>
-      </c>
-      <c r="C9" t="str">
-        <v>upg-frost</v>
+        <v>buff</v>
+      </c>
+      <c r="C9">
+        <v>2601</v>
       </c>
       <c r="D9" t="str">
-        <v>FrostOnHitEffect</v>
+        <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
+        <v>暴击直觉</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
       <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9">
-        <v>50</v>
+        <v>CritRate-Value-Buff</v>
+      </c>
+      <c r="I9">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>frostBuffId=8101;frostSlowPerStack=0.15;frostDuration=3;frostMaxStack=5</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>lightning-arrow</v>
+        <v>swift-step</v>
       </c>
       <c r="B10" t="str">
-        <v>hit_effect</v>
-      </c>
-      <c r="C10" t="str">
-        <v>upg-chain</v>
+        <v>buff</v>
+      </c>
+      <c r="C10">
+        <v>2602</v>
       </c>
       <c r="D10" t="str">
-        <v>ChainLightningEffect</v>
+        <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
+        <v>疾风步</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
       <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10">
-        <v>80</v>
+        <v>MoveSpeed-Mul-Buff</v>
+      </c>
+      <c r="I10">
+        <v>0.2</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>chance=0.25;jumps=3;chainRatio=0.5;chainDecay=0.7;chainRange=300</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>auto-fire-1</v>
+        <v>multi-shot</v>
       </c>
       <c r="B11" t="str">
-        <v>shoot_policy</v>
-      </c>
-      <c r="C11" t="str">
-        <v/>
+        <v>buff</v>
+      </c>
+      <c r="C11">
+        <v>2103</v>
       </c>
       <c r="D11" t="str">
-        <v>AutoShoot</v>
+        <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
+        <v>多重射击</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
       </c>
       <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
+        <v>ExtraProjectiles-Value-Buff</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
-      <c r="K11">
-        <v>1</v>
+      <c r="K11" t="str">
+        <v/>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -1176,37 +1498,37 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>auto-fire-2</v>
+        <v>pierce-shot</v>
       </c>
       <c r="B12" t="str">
-        <v>shoot_policy</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
+        <v>buff</v>
+      </c>
+      <c r="C12">
+        <v>2104</v>
       </c>
       <c r="D12" t="str">
-        <v>AutoShoot</v>
+        <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
+        <v>穿透射击</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
       <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
+        <v>PierceCount-Value-Buff</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
-      <c r="K12">
-        <v>2</v>
+      <c r="K12" t="str">
+        <v/>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1214,16 +1536,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>auto-fire-3</v>
+        <v>lightning-arrow</v>
       </c>
       <c r="B13" t="str">
-        <v>shoot_policy</v>
+        <v>hit_effect</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>upg-chain</v>
       </c>
       <c r="D13" t="str">
-        <v>AutoShoot</v>
+        <v>ChainLightningEffect</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -1240,31 +1562,31 @@
       <c r="I13" t="str">
         <v/>
       </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13">
-        <v>3</v>
+      <c r="J13">
+        <v>80</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>chance=1;jumps=3;chainRatio=0.5;chainDecay=0.7;chainRange=300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>scorching-pierce</v>
+        <v>barrage-shot</v>
       </c>
       <c r="B14" t="str">
         <v>buff</v>
       </c>
       <c r="C14">
-        <v>7201</v>
+        <v>2001</v>
       </c>
       <c r="D14" t="str">
         <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E14" t="str">
-        <v>灼热穿刺·穿透</v>
+        <v>弹幕射手</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1273,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="str">
-        <v>PierceCount-Value-Buff</v>
+        <v>ExtraProjectiles-Value-Buff</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1290,45 +1612,577 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>scorching-pierce</v>
+        <v>spread-mode</v>
       </c>
       <c r="B15" t="str">
-        <v>hit_effect</v>
-      </c>
-      <c r="C15" t="str">
-        <v>upg-scorching-burn</v>
+        <v>buff</v>
+      </c>
+      <c r="C15">
+        <v>2002</v>
       </c>
       <c r="D15" t="str">
-        <v>BurnOnHitEffect</v>
+        <v>SimpleAttrBuffEffect</v>
       </c>
       <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
+        <v>扫射模式</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
       </c>
       <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15">
+        <v>SpreadAngle-Value-Buff</v>
+      </c>
+      <c r="I15">
         <v>45</v>
       </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>burnRatio=0.4;burnBuffId=8003;burnDuration=5</v>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>chain-bounce</v>
+      </c>
+      <c r="B16" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C16">
+        <v>2401</v>
+      </c>
+      <c r="D16" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E16" t="str">
+        <v>连锁弹射</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="str">
+        <v>BounceCount-Value-Buff</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>long-range</v>
+      </c>
+      <c r="B17" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C17">
+        <v>2603</v>
+      </c>
+      <c r="D17" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E17" t="str">
+        <v>远程瞄准</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="str">
+        <v>AttackRange-Mul-Buff</v>
+      </c>
+      <c r="I17">
+        <v>0.5</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>rapid-fire-2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C18">
+        <v>2111</v>
+      </c>
+      <c r="D18" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E18" t="str">
+        <v>急速连射 II</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="str">
+        <v>AttackSpeed-Mul-Buff</v>
+      </c>
+      <c r="I18">
+        <v>0.3</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>sharp-arrow-2</v>
+      </c>
+      <c r="B19" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C19">
+        <v>2211</v>
+      </c>
+      <c r="D19" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E19" t="str">
+        <v>锐利箭头 II</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Attack-Mul-Buff</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>infinite-pierce</v>
+      </c>
+      <c r="B20" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C20">
+        <v>2400</v>
+      </c>
+      <c r="D20" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E20" t="str">
+        <v>无限穿透</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="str">
+        <v>PierceCount-Value-Buff</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>homing-instinct</v>
+      </c>
+      <c r="B21" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C21">
+        <v>2404</v>
+      </c>
+      <c r="D21" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E21" t="str">
+        <v>追猎本能</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="str">
+        <v>HomingStrength-Value-Buff</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>barrage-shot-2</v>
+      </c>
+      <c r="B22" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C22">
+        <v>2011</v>
+      </c>
+      <c r="D22" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E22" t="str">
+        <v>弹幕射手 II</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="str">
+        <v>ExtraProjectiles-Value-Buff</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>chain-bounce-2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C23">
+        <v>2411</v>
+      </c>
+      <c r="D23" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E23" t="str">
+        <v>连锁弹射 II</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="str">
+        <v>BounceCount-Value-Buff</v>
+      </c>
+      <c r="I23">
+        <v>6</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>crit-storm</v>
+      </c>
+      <c r="B24" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C24">
+        <v>2302</v>
+      </c>
+      <c r="D24" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E24" t="str">
+        <v>暴击风暴·概率</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="str">
+        <v>CritRate-Value-Buff</v>
+      </c>
+      <c r="I24">
+        <v>0.25</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>crit-storm</v>
+      </c>
+      <c r="B25" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C25">
+        <v>2312</v>
+      </c>
+      <c r="D25" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E25" t="str">
+        <v>暴击风暴·伤害</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="str">
+        <v>CritDmg-Value-Buff</v>
+      </c>
+      <c r="I25">
+        <v>0.5</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>executioner</v>
+      </c>
+      <c r="B26" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C26">
+        <v>2303</v>
+      </c>
+      <c r="D26" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E26" t="str">
+        <v>处刑之箭</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Attack-Mul-Buff</v>
+      </c>
+      <c r="I26">
+        <v>0.8</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>rapid-fire-3</v>
+      </c>
+      <c r="B27" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C27">
+        <v>2121</v>
+      </c>
+      <c r="D27" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E27" t="str">
+        <v>急速连射 III</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="str">
+        <v>AttackSpeed-Mul-Buff</v>
+      </c>
+      <c r="I27">
+        <v>0.5</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>sharp-arrow-3</v>
+      </c>
+      <c r="B28" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C28">
+        <v>2221</v>
+      </c>
+      <c r="D28" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E28" t="str">
+        <v>锐利箭头 III</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Attack-Mul-Buff</v>
+      </c>
+      <c r="I28">
+        <v>0.8</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>lifesteal-2</v>
+      </c>
+      <c r="B29" t="str">
+        <v>buff</v>
+      </c>
+      <c r="C29">
+        <v>2212</v>
+      </c>
+      <c r="D29" t="str">
+        <v>SimpleAttrBuffEffect</v>
+      </c>
+      <c r="E29" t="str">
+        <v>生命汲取 II</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="str">
+        <v>LifestealRate-Value-Buff</v>
+      </c>
+      <c r="I29">
+        <v>0.15</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
   </ignoredErrors>
 </worksheet>
 </file>